--- a/test/fixtures/xlsx/array-foreign/array-foreign.xlsx
+++ b/test/fixtures/xlsx/array-foreign/array-foreign.xlsx
@@ -128,14 +128,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:I9"/>
+  <dimension ref="B2:L9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -143,7 +143,7 @@
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -157,13 +157,13 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>2</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -177,13 +177,13 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
         <v>3</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -197,13 +197,13 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
+      <c r="J6" t="s">
         <v>4</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>19</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -217,13 +217,13 @@
       <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" t="s">
         <v>20</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -237,13 +237,13 @@
       <c r="D8" t="s">
         <v>6</v>
       </c>
-      <c r="G8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -257,13 +257,13 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="G9" t="s">
+      <c r="J9" t="s">
         <v>12</v>
       </c>
-      <c r="H9" t="s">
+      <c r="K9" t="s">
         <v>12</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>23</v>
       </c>
     </row>

--- a/test/fixtures/xlsx/array-foreign/array-foreign.xlsx
+++ b/test/fixtures/xlsx/array-foreign/array-foreign.xlsx
@@ -12,38 +12,47 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
-  <si>
-    <t xml:space="preserve">~~table:Target~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+  <si>
+    <t xml:space="preserve">:table Target</t>
   </si>
   <si>
     <t xml:space="preserve">Reference target.</t>
   </si>
   <si>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
     <t xml:space="preserve">Note</t>
   </si>
   <si>
@@ -59,7 +68,7 @@
     <t xml:space="preserve">first</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Holder~~</t>
+    <t xml:space="preserve">:table Holder</t>
   </si>
   <si>
     <t xml:space="preserve">Declares an array of references.</t>
@@ -68,13 +77,10 @@
     <t xml:space="preserve">Targets</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign Target[]</t>
+  </si>
+  <si>
     <t xml:space="preserve">unsupported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign[]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target</t>
   </si>
   <si>
     <t xml:space="preserve">Label</t>
@@ -128,68 +134,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:L9"/>
+  <dimension ref="B2:M7"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L4" t="s">
         <v>21</v>
       </c>
+      <c r="M4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
       </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -197,74 +239,40 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
       <c r="J6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L6" t="s">
         <v>9</v>
       </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" t="s">
-        <v>23</v>
+        <v>15</v>
+      </c>
+      <c r="M7" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/xlsx/array-foreign/array-foreign.xlsx
+++ b/test/fixtures/xlsx/array-foreign/array-foreign.xlsx
@@ -6,13 +6,14 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Bad" sheetId="1" r:id="rId3"/>
+    <sheet name="Refs" sheetId="1" r:id="rId3"/>
+    <sheet name="Holder" sheetId="2" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
   <si>
     <t xml:space="preserve">:table Target</t>
   </si>
@@ -68,10 +69,28 @@
     <t xml:space="preserve">first</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">second</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">three</t>
+  </si>
+  <si>
+    <t xml:space="preserve">third</t>
+  </si>
+  <si>
     <t xml:space="preserve">:table Holder</t>
   </si>
   <si>
-    <t xml:space="preserve">Declares an array of references.</t>
+    <t xml:space="preserve">Arrays of references, written in one cell each.</t>
   </si>
   <si>
     <t xml:space="preserve">Targets</t>
@@ -80,7 +99,16 @@
     <t xml:space="preserve">foreign Target[]</t>
   </si>
   <si>
-    <t xml:space="preserve">unsupported</t>
+    <t xml:space="preserve">a list of rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign Target.Note[]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a list of one of that row's values</t>
   </si>
   <si>
     <t xml:space="preserve">Label</t>
@@ -89,7 +117,22 @@
     <t xml:space="preserve">label</t>
   </si>
   <si>
-    <t xml:space="preserve">a</t>
+    <t xml:space="preserve">1;2;3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">three and two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">one and one</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">none and none</t>
   </si>
 </sst>
 </file>
@@ -134,7 +177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:M7"/>
+  <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -144,12 +187,6 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
@@ -164,18 +201,6 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="J3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="4">
       <c r="B4" t="s">
@@ -190,18 +215,6 @@
       <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="5">
       <c r="B5" t="s">
@@ -216,18 +229,6 @@
       <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="J5" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>24</v>
-      </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
@@ -242,18 +243,6 @@
       <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="J6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K6" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="7">
       <c r="C7" t="s">
@@ -265,14 +254,155 @@
       <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="K7" t="s">
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="B2:F9"/>
+  <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="L7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>25</v>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
